--- a/Examples/Geo1_ms.xlsx
+++ b/Examples/Geo1_ms.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joela\Documents\GitHub\joecga4\pyOMA2\Examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\catolica\Documents\GitHub\pyOMA2\Examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E985AE9F-61F4-4557-8072-F236D1D0F811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{239D3FD3-7DB5-43CA-A3A1-49071C9EC557}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="sensors names" sheetId="19" r:id="rId1"/>
@@ -21,7 +20,7 @@
     <sheet name="BG lines" sheetId="23" r:id="rId6"/>
     <sheet name="BG surfaces" sheetId="24" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,14 +39,14 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{96C51F0F-F958-4A59-A9F6-E4F71EEE73A2}" keepAlive="1" name="Query - hctlines" description="Connessione alla query 'hctlines' nella cartella di lavoro." type="5" refreshedVersion="8" background="1" saveData="1">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" keepAlive="1" name="Query - hctlines" description="Connessione alla query 'hctlines' nella cartella di lavoro." type="5" refreshedVersion="8" background="1" saveData="1">
     <dbPr connection="Provider=Microsoft.Mashup.OleDb.1;Data Source=$Workbook$;Location=hctlines;Extended Properties=&quot;&quot;" command="SELECT * FROM [hctlines]"/>
   </connection>
-  <connection id="2" xr16:uid="{3B096521-211B-426C-9A21-DBD1CB62EFFE}" keepAlive="1" name="Query - hctnodes" description="Connessione alla query 'hctnodes' nella cartella di lavoro." type="5" refreshedVersion="8" background="1" saveData="1">
+  <connection id="2" keepAlive="1" name="Query - hctnodes" description="Connessione alla query 'hctnodes' nella cartella di lavoro." type="5" refreshedVersion="8" background="1" saveData="1">
     <dbPr connection="Provider=Microsoft.Mashup.OleDb.1;Data Source=$Workbook$;Location=hctnodes;Extended Properties=&quot;&quot;" command="SELECT * FROM [hctnodes]"/>
   </connection>
-  <connection id="3" xr16:uid="{F07D8490-B285-4A97-8FB6-27F9608C237B}" keepAlive="1" name="Query - Tabella4" description="Connessione alla query 'Tabella4' nella cartella di lavoro." type="5" refreshedVersion="8" background="1" saveData="1">
+  <connection id="3" keepAlive="1" name="Query - Tabella4" description="Connessione alla query 'Tabella4' nella cartella di lavoro." type="5" refreshedVersion="8" background="1" saveData="1">
     <dbPr connection="Provider=Microsoft.Mashup.OleDb.1;Data Source=$Workbook$;Location=Tabella4;Extended Properties=&quot;&quot;" command="SELECT * FROM [Tabella4]"/>
   </connection>
 </connections>
@@ -284,7 +283,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -652,9 +651,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B5F60D-4600-45C6-9F9B-CE573204C65F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y3"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="16384" width="9.140625" style="2"/>
@@ -898,9 +897,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A63EEFAF-45DA-4A18-AEC3-F6C99055E21F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" customWidth="1"/>
     <col min="2" max="16384" width="9.140625" style="2"/>
@@ -1481,9 +1480,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F8647A2-283F-45ED-8CDC-E05E1BE90853}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K40"/>
-  <sheetFormatPr defaultColWidth="5.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="5.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="16384" width="5.85546875" style="2"/>
@@ -1536,7 +1535,7 @@
         <v>68</v>
       </c>
       <c r="B4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
@@ -1578,7 +1577,7 @@
         <v>71</v>
       </c>
       <c r="B7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
@@ -1620,7 +1619,7 @@
         <v>74</v>
       </c>
       <c r="B10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="2">
         <v>0</v>
@@ -1662,7 +1661,7 @@
         <v>38</v>
       </c>
       <c r="B13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="2">
         <v>0</v>
@@ -1704,7 +1703,7 @@
         <v>41</v>
       </c>
       <c r="B16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
@@ -1747,7 +1746,7 @@
         <v>44</v>
       </c>
       <c r="B19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" s="2">
         <v>0</v>
@@ -1789,7 +1788,7 @@
         <v>47</v>
       </c>
       <c r="B22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
@@ -1831,7 +1830,7 @@
         <v>50</v>
       </c>
       <c r="B25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" s="2">
         <v>0</v>
@@ -1873,7 +1872,7 @@
         <v>53</v>
       </c>
       <c r="B28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -1915,7 +1914,7 @@
         <v>56</v>
       </c>
       <c r="B31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -1957,7 +1956,7 @@
         <v>59</v>
       </c>
       <c r="B34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
@@ -1999,7 +1998,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -2041,7 +2040,7 @@
         <v>65</v>
       </c>
       <c r="B40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -2057,9 +2056,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B519F1-6E02-432D-A33C-937A98D77CCB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2411,9 +2410,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D4466D4-9D9C-462B-90FB-DE58C3441D80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="16384" width="9.140625" style="2"/>
@@ -2624,9 +2623,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F59F39B5-D487-4E58-BF61-A925B720FB4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2978,9 +2977,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{017C2B43-5A27-4A12-963B-B018A4C343EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
